--- a/data.mn/public/datasets/meat-production-by-region.xlsx
+++ b/data.mn/public/datasets/meat-production-by-region.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,337 +414,741 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>year</t>
         </is>
       </c>
-      <c r="B1" t="n">
-        <v>2010</v>
-      </c>
-      <c r="C1" t="n">
-        <v>2011</v>
-      </c>
-      <c r="D1" t="n">
-        <v>2012</v>
-      </c>
-      <c r="E1" t="n">
-        <v>2013</v>
-      </c>
-      <c r="F1" t="n">
-        <v>2014</v>
-      </c>
-      <c r="G1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="H1" t="n">
-        <v>2016</v>
-      </c>
-      <c r="I1" t="n">
-        <v>2017</v>
-      </c>
-      <c r="J1" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K1" t="n">
-        <v>2019</v>
-      </c>
-      <c r="L1" t="n">
-        <v>2020</v>
-      </c>
-      <c r="M1" t="n">
-        <v>2021</v>
-      </c>
-      <c r="N1" t="n">
-        <v>2022</v>
-      </c>
-      <c r="O1" t="n">
-        <v>2023</v>
-      </c>
-      <c r="P1" t="n">
-        <v>2024</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Central region</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>74919.5</v>
-      </c>
-      <c r="C2" t="n">
-        <v>66195.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>68650</v>
-      </c>
-      <c r="E2" t="n">
-        <v>76901.89999999999</v>
-      </c>
-      <c r="F2" t="n">
-        <v>74263.60000000001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>118371.9</v>
-      </c>
-      <c r="H2" t="n">
-        <v>108614.3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>107362.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>121236.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>120970.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>152123.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>135806</v>
-      </c>
-      <c r="N2" t="n">
-        <v>158188.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>187717.5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>116421.5</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>167509.088</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Eastern region</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>30486</v>
-      </c>
-      <c r="C3" t="n">
-        <v>48816.7</v>
-      </c>
-      <c r="D3" t="n">
-        <v>48601.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>48400.8</v>
-      </c>
-      <c r="F3" t="n">
-        <v>47545.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>64695.4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>71545.2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>43860.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>82776.39999999999</v>
-      </c>
-      <c r="K3" t="n">
-        <v>95405.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>106995</v>
-      </c>
-      <c r="M3" t="n">
-        <v>84609.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>106085.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>128377.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>66796.7</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>94900.167</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Khangai region</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>82585.7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>90042.89999999999</v>
-      </c>
-      <c r="D4" t="n">
-        <v>95589.10000000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>111459.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>107655.9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>168339.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>137929.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>175058.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>184093.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>205933.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>320043.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>174511.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>207700.1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>230885.7</v>
-      </c>
-      <c r="P4" t="n">
-        <v>176245.5</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>265663.375</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Ulaanbaatar</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>5960.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5652.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5198.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5692.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4854.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8709.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7647.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8626.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9532.700000000001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>8094.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7410.6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9341.299999999999</v>
-      </c>
-      <c r="N5" t="n">
-        <v>9161.200000000001</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6719.1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6410.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2588.572</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Western region</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2" t="n">
+        <v>74919.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>82585.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5960.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>47118.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>66195.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48816.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>90042.89999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5652.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>40640</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>68650</v>
+      </c>
+      <c r="C4" t="n">
+        <v>48601.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>95589.10000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5198.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>45375.9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>76901.89999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>48400.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>111459.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5692.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56826.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2014</v>
+      </c>
       <c r="B6" t="n">
-        <v>47118.5</v>
+        <v>74263.60000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>40640</v>
+        <v>47545.1</v>
       </c>
       <c r="D6" t="n">
-        <v>45375.9</v>
+        <v>107655.9</v>
       </c>
       <c r="E6" t="n">
-        <v>56826.4</v>
+        <v>4854.5</v>
       </c>
       <c r="F6" t="n">
         <v>57336.7</v>
       </c>
-      <c r="G6" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="n">
+        <v>118371.9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>64695.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>168339.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8709.6</v>
+      </c>
+      <c r="F7" t="n">
         <v>88039.8</v>
       </c>
-      <c r="H6" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108614.3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>71545.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>137929.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7647.1</v>
+      </c>
+      <c r="F8" t="n">
         <v>75848.7</v>
       </c>
-      <c r="I6" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107362.9</v>
+      </c>
+      <c r="C9" t="n">
+        <v>43860.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>175058.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8626.4</v>
+      </c>
+      <c r="F9" t="n">
         <v>91259.89999999999</v>
       </c>
-      <c r="J6" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>121236.9</v>
+      </c>
+      <c r="C10" t="n">
+        <v>82776.39999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>184093.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9532.700000000001</v>
+      </c>
+      <c r="F10" t="n">
         <v>117543.1</v>
       </c>
-      <c r="K6" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B11" t="n">
+        <v>120970.8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>95405.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>205933.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8094.4</v>
+      </c>
+      <c r="F11" t="n">
         <v>113413</v>
       </c>
-      <c r="L6" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="n">
+        <v>152123.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>106995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>320043.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7410.6</v>
+      </c>
+      <c r="F12" t="n">
         <v>159588.5</v>
       </c>
-      <c r="M6" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>135806</v>
+      </c>
+      <c r="C13" t="n">
+        <v>84609.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>174511.1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9341.299999999999</v>
+      </c>
+      <c r="F13" t="n">
         <v>102702.1</v>
       </c>
-      <c r="N6" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>158188.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>106085.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>207700.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9161.200000000001</v>
+      </c>
+      <c r="F14" t="n">
         <v>169011.3</v>
       </c>
-      <c r="O6" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>187717.5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>128377.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>230885.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6719.1</v>
+      </c>
+      <c r="F15" t="n">
         <v>114859.6</v>
       </c>
-      <c r="P6" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="n">
+        <v>116421.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>66796.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>176245.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6410.1</v>
+      </c>
+      <c r="F16" t="n">
         <v>87262.89999999999</v>
       </c>
-      <c r="Q6" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>167509.088</v>
+      </c>
+      <c r="C17" t="n">
+        <v>94900.167</v>
+      </c>
+      <c r="D17" t="n">
+        <v>265663.375</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2588.572</v>
+      </c>
+      <c r="F17" t="n">
         <v>169211.179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Баруун бүс</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Зүүн бүс</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Төвийн бүс</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Улаанбаатар</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Хангайн бүс</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2" t="n">
+        <v>47118.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>74919.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5960.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>82585.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="n">
+        <v>40640</v>
+      </c>
+      <c r="C3" t="n">
+        <v>48816.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>66195.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5652.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>90042.89999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="n">
+        <v>45375.9</v>
+      </c>
+      <c r="C4" t="n">
+        <v>48601.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>68650</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5198.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>95589.10000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56826.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>48400.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>76901.89999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5692.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>111459.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57336.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>47545.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>74263.60000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4854.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>107655.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88039.8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>64695.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>118371.9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8709.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>168339.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75848.7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>71545.2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>108614.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7647.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>137929.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91259.89999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>43860.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>107362.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8626.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>175058.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="n">
+        <v>117543.1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>82776.39999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>121236.9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9532.700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>184093.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B11" t="n">
+        <v>113413</v>
+      </c>
+      <c r="C11" t="n">
+        <v>95405.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>120970.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8094.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>205933.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="n">
+        <v>159588.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>106995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>152123.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>7410.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>320043.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102702.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>84609.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>135806</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9341.299999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>174511.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="n">
+        <v>169011.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>106085.2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>158188.1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9161.200000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>207700.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="n">
+        <v>114859.6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>128377.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>187717.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6719.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>230885.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="n">
+        <v>87262.89999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>66796.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>116421.5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>6410.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>176245.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>169211.179</v>
+      </c>
+      <c r="C17" t="n">
+        <v>94900.167</v>
+      </c>
+      <c r="D17" t="n">
+        <v>167509.088</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2588.572</v>
+      </c>
+      <c r="F17" t="n">
+        <v>265663.375</v>
       </c>
     </row>
   </sheetData>
